--- a/artfynd/A 9012-2025 artfynd.xlsx
+++ b/artfynd/A 9012-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>76544476</v>
+        <v>76544472</v>
       </c>
       <c r="B2" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57945</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100110</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -722,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>712697.1135625733</v>
+        <v>712697</v>
       </c>
       <c r="R2" t="n">
-        <v>7062290.145318811</v>
+        <v>7062290</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -757,7 +752,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:09</t>
+          <t>07:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +762,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:09</t>
+          <t>07:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,15 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>76552772</v>
+        <v>76544476</v>
       </c>
       <c r="B3" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>712690.2169632014</v>
+        <v>712697</v>
       </c>
       <c r="R3" t="n">
-        <v>7062273.181776972</v>
+        <v>7062290</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,22 +861,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-03-24</t>
+          <t>2019-03-23</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-03-24</t>
+          <t>2019-03-23</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,6 +900,120 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>76552772</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Nordmaling, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>712690</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7062273</v>
+      </c>
+      <c r="S4" t="n">
+        <v>6</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2019-03-24</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2019-03-24</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anders Berg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anders Berg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9012-2025 artfynd.xlsx
+++ b/artfynd/A 9012-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76544472</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76544476</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,8 +1029,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76552772</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>